--- a/artfynd/A 62103-2022 artfynd.xlsx
+++ b/artfynd/A 62103-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62103-2022 artfynd.xlsx
+++ b/artfynd/A 62103-2022 artfynd.xlsx
@@ -3901,7 +3901,7 @@
         <v>76813202</v>
       </c>
       <c r="B29" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398302.7099942484</v>
+        <v>398303</v>
       </c>
       <c r="R29" t="n">
-        <v>6741978.631116337</v>
+        <v>6741979</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3979,19 +3979,9 @@
           <t>2019-04-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2019-04-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 62103-2022 artfynd.xlsx
+++ b/artfynd/A 62103-2022 artfynd.xlsx
@@ -3901,7 +3901,7 @@
         <v>76813202</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
